--- a/data/scorecard/FO_Market_Scorecard_Polo_OneSheet_v5.xlsx
+++ b/data/scorecard/FO_Market_Scorecard_Polo_OneSheet_v5.xlsx
@@ -26,7 +26,7 @@
     <definedName name="PrevLiq">Market_Scorecard_Polo!$I$9</definedName>
     <definedName name="Turnover">Market_Scorecard_Polo!$C$43</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1768,8 +1768,8 @@
       <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="65" t="s">
-        <v>33</v>
+      <c r="E8" s="65">
+        <v>0</v>
       </c>
       <c r="F8" s="56" t="str">
         <f>IF(COUNT(D35:D38)=0,"",IF(AVERAGE(D35:D38)&lt;4,"Tight",
@@ -2413,8 +2413,10 @@
       </c>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" t="s">
-        <v>133</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Flow</t>
+        </is>
       </c>
       <c r="B27" t="s">
         <v>69</v>
